--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.77329993764157</v>
+        <v>7.600661239866755</v>
       </c>
       <c r="D2" t="n">
-        <v>18.53495920896925</v>
+        <v>3.011930871457503</v>
       </c>
       <c r="E2" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F2" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.11524376736998</v>
+        <v>7.331227112197621</v>
       </c>
       <c r="D3" t="n">
-        <v>42.20636834484354</v>
+        <v>6.858534856037076</v>
       </c>
       <c r="E3" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F3" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.91645211034393</v>
+        <v>5.511423467930889</v>
       </c>
       <c r="D4" t="n">
-        <v>29.21779713737087</v>
+        <v>4.747892034822766</v>
       </c>
       <c r="E4" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F4" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.87499051421228</v>
+        <v>6.967185958559496</v>
       </c>
       <c r="D5" t="n">
-        <v>33.18167860761942</v>
+        <v>5.392022773738155</v>
       </c>
       <c r="E5" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F5" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.58577219838882</v>
+        <v>4.645187982238183</v>
       </c>
       <c r="D6" t="n">
-        <v>30.12626132618601</v>
+        <v>4.895517465505226</v>
       </c>
       <c r="E6" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F6" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.22622004678064</v>
+        <v>8.324260757601854</v>
       </c>
       <c r="D7" t="n">
-        <v>32.49724822040744</v>
+        <v>5.280802835816209</v>
       </c>
       <c r="E7" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F7" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.02225724326634</v>
+        <v>5.36611680203078</v>
       </c>
       <c r="D8" t="n">
-        <v>25.00903411101308</v>
+        <v>4.063968043039626</v>
       </c>
       <c r="E8" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F8" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.23031368598508</v>
+        <v>5.724925973972576</v>
       </c>
       <c r="D9" t="n">
-        <v>32.21146954047299</v>
+        <v>5.234363800326861</v>
       </c>
       <c r="E9" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F9" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.60276723470464</v>
+        <v>3.022949675639504</v>
       </c>
       <c r="D10" t="n">
-        <v>18.76470082169446</v>
+        <v>3.04926388352535</v>
       </c>
       <c r="E10" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F10" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.95408002375053</v>
+        <v>5.517538003859461</v>
       </c>
       <c r="D11" t="n">
-        <v>34.74284348182245</v>
+        <v>5.645712065796148</v>
       </c>
       <c r="E11" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F11" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.79533405826262</v>
+        <v>2.241741784467675</v>
       </c>
       <c r="D12" t="n">
-        <v>16.87108194997218</v>
+        <v>2.741550816870479</v>
       </c>
       <c r="E12" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F12" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.31503179978003</v>
+        <v>4.438692667464255</v>
       </c>
       <c r="D13" t="n">
-        <v>27.47416377336696</v>
+        <v>4.464551613172132</v>
       </c>
       <c r="E13" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F13" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.28404259910801</v>
+        <v>5.733656922355051</v>
       </c>
       <c r="D14" t="n">
-        <v>38.97931106874803</v>
+        <v>6.334138048671555</v>
       </c>
       <c r="E14" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F14" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>14.81674828812145</v>
+        <v>2.407721596819735</v>
       </c>
       <c r="D15" t="n">
-        <v>15.33341272788863</v>
+        <v>2.491679568281903</v>
       </c>
       <c r="E15" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F15" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.02580815803015</v>
+        <v>4.716693825679899</v>
       </c>
       <c r="D16" t="n">
-        <v>28.50777633857233</v>
+        <v>4.632513655018005</v>
       </c>
       <c r="E16" t="n">
-        <v>10.80270102744666</v>
+        <v>1.755438916960081</v>
       </c>
       <c r="F16" t="n">
-        <v>7.773496588754886</v>
+        <v>1.263193195672669</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
